--- a/Deliverable/BOM/(5 Boards)Digikey-Interface-Board-BOM.xlsx
+++ b/Deliverable/BOM/(5 Boards)Digikey-Interface-Board-BOM.xlsx
@@ -1,15 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E777637-341F-41EE-87D2-32D123000F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23325" windowHeight="9795"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -202,9 +218,6 @@
     <t>910K</t>
   </si>
   <si>
-    <t>Header</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 10POS 2.54MM</t>
   </si>
   <si>
@@ -233,20 +246,19 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Connector</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,27 +291,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
@@ -308,185 +299,44 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
+      <strike/>
       <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,194 +355,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="37">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1074,267 +738,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="36" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1344,281 +763,178 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1876,536 +1192,537 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="80.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="79.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="27.2857142857143" customWidth="1"/>
-    <col min="7" max="7" width="14.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
-    <col min="9" max="9" width="14.4285714285714" customWidth="1"/>
-    <col min="10" max="10" width="18.2857142857143" customWidth="1"/>
-    <col min="11" max="11" width="10.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12.4285714285714" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15" ht="15.75">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="33"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="10"/>
     </row>
-    <row r="2" ht="15.75" spans="1:15">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:15">
-      <c r="A3" s="6">
+    <row r="3" spans="1:15">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="20">
         <v>5</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="21">
         <f>J3*5</f>
         <v>25</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="37">
-        <v>0.029</v>
-      </c>
-      <c r="N3" s="38">
+      <c r="M3" s="23">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N3" s="23">
         <f>M3*K3</f>
-        <v>0.725</v>
-      </c>
-      <c r="O3" s="39"/>
+        <v>0.72500000000000009</v>
+      </c>
+      <c r="O3" s="24"/>
     </row>
-    <row r="4" ht="15.75" spans="1:15">
-      <c r="A4" s="6">
+    <row r="4" spans="1:15">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="65" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="66" t="s">
+      <c r="F4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="27">
         <v>2</v>
       </c>
-      <c r="K4" s="40">
+      <c r="K4" s="28">
         <f t="shared" ref="K4:K11" si="0">J4*5</f>
         <v>10</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="42">
+      <c r="M4" s="30">
         <v>0.08</v>
       </c>
-      <c r="N4" s="43">
+      <c r="N4" s="30">
         <f t="shared" ref="N4:N11" si="1">M4*K4</f>
         <v>0.8</v>
       </c>
-      <c r="O4" s="44"/>
+      <c r="O4" s="31"/>
     </row>
-    <row r="5" ht="15.75" spans="1:15">
-      <c r="A5" s="6">
+    <row r="5" spans="1:15">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="65" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="66" t="s">
+      <c r="E5" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="66" t="s">
+      <c r="F5" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="27">
         <v>1</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="28">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="41" t="s">
+      <c r="L5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="30">
         <v>0.156</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="30">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
-      <c r="O5" s="44"/>
+      <c r="O5" s="31"/>
     </row>
-    <row r="6" ht="15.75" spans="1:15">
-      <c r="A6" s="6">
+    <row r="6" spans="1:15">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="68" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="70" t="s">
+      <c r="G6" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="71" t="s">
+      <c r="H6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="35">
         <v>1</v>
       </c>
-      <c r="K6" s="45">
+      <c r="K6" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L6" s="46" t="s">
+      <c r="L6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="38">
         <v>0.38</v>
       </c>
-      <c r="N6" s="48">
+      <c r="N6" s="38">
         <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
-      <c r="O6" s="49"/>
+      <c r="O6" s="39"/>
     </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="6">
+    <row r="7" spans="1:15" ht="25.5">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="73" t="s">
+      <c r="G7" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="42">
         <v>4</v>
       </c>
-      <c r="K7" s="50">
+      <c r="K7" s="43">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L7" s="51" t="s">
+      <c r="L7" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="52">
-        <v>0.486</v>
-      </c>
-      <c r="N7" s="48">
+      <c r="M7" s="57">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="N7" s="38">
         <f t="shared" si="1"/>
-        <v>9.72</v>
-      </c>
-      <c r="O7" s="53"/>
+        <v>9.7199999999999989</v>
+      </c>
+      <c r="O7" s="44"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A8" s="6">
+    <row r="8" spans="1:15" s="1" customFormat="1">
+      <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="D8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="62" t="s">
+      <c r="I8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="20">
         <v>3</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="21">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="37">
-        <v>0.016</v>
-      </c>
-      <c r="N8" s="38">
+      <c r="M8" s="23">
+        <v>1.6E-2</v>
+      </c>
+      <c r="N8" s="23">
         <f t="shared" si="1"/>
         <v>0.24</v>
       </c>
-      <c r="O8" s="39"/>
+      <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="15.75" spans="1:15">
-      <c r="A9" s="6">
+    <row r="9" spans="1:15" ht="25.5">
+      <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="68" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="76" t="s">
+      <c r="F9" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="69" t="s">
+      <c r="I9" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="35">
         <v>1</v>
       </c>
-      <c r="K9" s="45">
+      <c r="K9" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L9" s="46" t="s">
+      <c r="L9" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="38">
         <v>0.1</v>
       </c>
-      <c r="N9" s="48">
+      <c r="N9" s="38">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="O9" s="49"/>
+      <c r="O9" s="39"/>
     </row>
-    <row r="10" ht="15.75" spans="1:15">
-      <c r="A10" s="6">
+    <row r="10" spans="1:15">
+      <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="77" t="s">
+      <c r="D10" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="78" t="s">
+      <c r="E10" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="78" t="s">
+      <c r="G10" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="78" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="79" t="s">
+      <c r="H10" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="50">
         <v>1</v>
       </c>
-      <c r="K10" s="54">
+      <c r="K10" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="55" t="s">
+      <c r="L10" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="56">
+      <c r="M10" s="53">
         <v>0.46</v>
       </c>
-      <c r="N10" s="57">
+      <c r="N10" s="53">
         <f t="shared" si="1"/>
-        <v>2.3</v>
-      </c>
-      <c r="O10" s="58"/>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="O10" s="54"/>
     </row>
-    <row r="11" ht="15.75" spans="1:15">
-      <c r="A11" s="6">
+    <row r="11" spans="1:15" ht="25.5">
+      <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="68" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="E11" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="71" t="s">
+      <c r="G11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="71" t="s">
+      <c r="H11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="71" t="s">
+      <c r="I11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="35">
         <v>1</v>
       </c>
-      <c r="K11" s="45">
+      <c r="K11" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L11" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="M11" s="47">
-        <v>1.15</v>
-      </c>
-      <c r="N11" s="48">
+      <c r="L11" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="M11" s="38">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N11" s="38">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="O11" s="49"/>
+      <c r="O11" s="39"/>
     </row>
-    <row r="12" ht="19.5" spans="7:14">
-      <c r="G12" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="N12" s="60">
+    <row r="12" spans="1:15" ht="18.75">
+      <c r="G12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="N12" s="7">
         <f>SUM(N3:N11)</f>
         <v>22.715</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="7:14">
-      <c r="G13" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="N13" s="60">
+    <row r="13" spans="1:15" ht="18.75">
+      <c r="G13" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="N13" s="7">
         <f>N12/5</f>
-        <v>4.543</v>
+        <v>4.5430000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +1743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8075f51b-85fe-4b82-99a4-f8b9281869d4}</x14:id>
+          <x14:id>{8075F51B-85FE-4B82-99A4-F8B9281869D4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2440,7 +1757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15d60ac5-9b89-492c-8909-06c2b35856dc}</x14:id>
+          <x14:id>{15D60AC5-9B89-492C-8909-06C2B35856DC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2458,22 +1775,22 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" display="Digikey"/>
-    <hyperlink ref="L4" r:id="rId2" display="Digikey"/>
-    <hyperlink ref="L5" r:id="rId3" display="Digikey"/>
-    <hyperlink ref="L6" r:id="rId4" display="Digikey"/>
-    <hyperlink ref="L10" r:id="rId5" display="Digikey"/>
-    <hyperlink ref="L8" r:id="rId6" display="Digikey"/>
-    <hyperlink ref="L9" r:id="rId7" display="Digikey"/>
-    <hyperlink ref="L7" r:id="rId8" display="Digikey"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="L10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="L8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="L9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="L7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8075f51b-85fe-4b82-99a4-f8b9281869d4}">
+          <x14:cfRule type="dataBar" id="{8075F51B-85FE-4B82-99A4-F8B9281869D4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2486,7 +1803,7 @@
           <xm:sqref>N13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15d60ac5-9b89-492c-8909-06c2b35856dc}">
+          <x14:cfRule type="dataBar" id="{15D60AC5-9B89-492C-8909-06C2B35856DC}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
